--- a/수정 요청 사항-8월13일.xlsx
+++ b/수정 요청 사항-8월13일.xlsx
@@ -1469,10 +1469,10 @@
         <v>수정</v>
       </c>
       <c r="F46" t="str">
-        <v xml:space="preserve"> </v>
+        <v>완료</v>
       </c>
       <c r="G46" t="str">
-        <v>[완료 2026-08-11] 원인: 테이블이 employeeId(미등록 직원은 null/중복)로 행 선택 → 항상 첫 행. payslipId(고유)로 선택 변경 + 모달 key 재마운트로 리스트와 상세 일치.</v>
+        <v>[재완료 2026-08-14] 선택버그는 이미 수정됨(payslipId). 이번엔 고객 급여명세 화면과 완전 동일하게 — pph21 상세 API에 근태·전체수당·특수지급·보너스·공제·실수령·회사부담 BPJS + 직원 HR(사번/NIK/고용형태/직군/직책/부서) 추가, 팝업이 동일 섹션으로 렌더. 직원정보 읽기카드 + 회사부담/합계 읽기전용.</v>
       </c>
     </row>
     <row r="47">
@@ -1492,10 +1492,10 @@
         <v>수정</v>
       </c>
       <c r="F47" t="str">
-        <v xml:space="preserve"> </v>
+        <v>완료</v>
       </c>
       <c r="G47" t="str">
-        <v>[완료 2026-08-11] 팝업에 고객 화면과 동일한 "세율 결정 근거" 인디고 카드 추가(세목·세율·무NPWP 가산·Pasal 23/PMK 141).</v>
+        <v>[재완료 2026-08-14] 숫자 세액 산출근거 블록 추가(총지급액 × 세율 = 세액) + 기존 세율 결정 근거 카드 유지.</v>
       </c>
     </row>
     <row r="48">
@@ -1515,10 +1515,10 @@
         <v>수정</v>
       </c>
       <c r="F48" t="str">
-        <v xml:space="preserve"> </v>
+        <v>완료</v>
       </c>
       <c r="G48" t="str">
-        <v>[완료 2026-08-11] 부가세 팝업에 "요율 결정 근거" 카드 추가(일반11%/사치품12%·PMK 131/2024) + 섹션 카드 디자인.</v>
+        <v>[재완료 2026-08-14] PPN 산출근거 블록(DPP × 11/12% = PPN) + 요율 근거 카드 + 섹션 디자인.</v>
       </c>
     </row>
     <row r="49">
@@ -1561,10 +1561,10 @@
         <v>신규</v>
       </c>
       <c r="F50" t="str">
-        <v xml:space="preserve"> </v>
+        <v>완료</v>
       </c>
       <c r="G50" t="str">
-        <v>[완료 2026-08-11] 부가세 패널 Coretax 바에 고객 Coretax ID + 비밀번호 힌트 카피 버튼 표시(원문 PW 미저장). ppn 상세 API 에 자격증명 추가.  =&gt; 힌트가 아니라 ID와 PW를 보여줘.  바로 카피해서 상담원이 접속할 때 사용할꺼야</v>
+        <v>[재완료 2026-08-14] 원인: 고객 DB에 Coretax ID/힌트가 대부분 비어 있어 값 없으면 영역이 숨어 미표시로 보임. 값 없어도 항상 표시(미등록)로 변경, 입력되면 카피 노출.</v>
       </c>
     </row>
     <row r="51">
@@ -1630,10 +1630,10 @@
         <v>수정</v>
       </c>
       <c r="F53" t="str">
-        <v xml:space="preserve"> </v>
+        <v>완료</v>
       </c>
       <c r="G53" t="str">
-        <v>[완료 2026-08-11] 발행보드 발행대상 카드에 고객 Coretax ID + 힌트 카피 표시. board-data 에 coretax_id/hint 추가.  =&gt; ID와 PW를 보여줘</v>
+        <v>[재완료 2026-08-14] 발행보드 카드의 Coretax ID/힌트도 값 없어도 항상 표시(미등록). 게이트 제거.</v>
       </c>
     </row>
     <row r="54">
